--- a/Assessment Questions/CDA/DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Various Data Reporting formats,/• Various Data Reporting formats,.xlsx
+++ b/Assessment Questions/CDA/DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Various Data Reporting formats,/• Various Data Reporting formats,.xlsx
@@ -1,168 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manfo\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19C9A1C3-BA65-401D-81A1-8E36261A5A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E120A525-CAFB-4323-BD76-DA249CC727BF}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
-  <si>
-    <t>Scenario,Column1,Column2,Column3,Column4,Column5</t>
-  </si>
-  <si>
-    <t>Scenario 1: Choosing the Right Report Format,,,,,</t>
-  </si>
-  <si>
-    <t>Questions,,,,,</t>
-  </si>
-  <si>
-    <t>Q1,Showing exact sales numbers for each product. Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Q2,Comparing sales across 5 regions visually. Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Q3,Executive overview of key metrics (sales, profit, customers). Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Q4,Showing monthly sales trend over 12 months. Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Q5,Detailed transaction list for audit purposes. Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Q6,Showing each product's percentage contribution to total sales. Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Q7,Comparing this year's sales vs last year's sales for each month. Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Q8,Showing stock levels for 50 products at a glance. Which format is best? Why?,,,,</t>
-  </si>
-  <si>
-    <t>Scenario 2: Weekly Sales Data,,,,,</t>
-  </si>
-  <si>
-    <t>Week,Product A,Product B,Product C,Product D,Total Sales</t>
-  </si>
-  <si>
-    <t>Week 1,1200,850,2100,950,5100</t>
-  </si>
-  <si>
-    <t>Week 2,1300,900,2200,1000,5400</t>
-  </si>
-  <si>
-    <t>Week 3,1250,880,2150,980,5260</t>
-  </si>
-  <si>
-    <t>Week 4,1350,920,2300,1020,5590</t>
-  </si>
-  <si>
-    <t>Q9,Create a table format report showing sales by product for each week.,,,,</t>
-  </si>
-  <si>
-    <t>Q10,Create a bar chart description showing total sales by week. Which week had the highest sales?,,,,</t>
-  </si>
-  <si>
-    <t>Q11,Create a line chart description showing sales trend for Product C over the 4 weeks.,,,,</t>
-  </si>
-  <si>
-    <t>Q12,Create a pie chart description showing each product's contribution to total sales for Week 4.,,,,</t>
-  </si>
-  <si>
-    <t>Q13,Create a dashboard description.,,,,</t>
-  </si>
-  <si>
-    <t>Q14,Which product had highest and lowest sales in Week 4?,,,,</t>
-  </si>
-  <si>
-    <t>Scenario 3: Expense Data,,,,,</t>
-  </si>
-  <si>
-    <t>Month,Rent,Salaries,Utilities,Marketing,Total</t>
-  </si>
-  <si>
-    <t>Jan,5000,15000,1200,2000,23200</t>
-  </si>
-  <si>
-    <t>Feb,5000,15000,1100,2500,23600</t>
-  </si>
-  <si>
-    <t>Mar,5000,16000,1300,3000,25300</t>
-  </si>
-  <si>
-    <t>Apr,5000,16000,1150,2800,24950</t>
-  </si>
-  <si>
-    <t>May,5000,16500,1250,3200,25950</t>
-  </si>
-  <si>
-    <t>Jun,5000,16500,1350,3500,26350</t>
-  </si>
-  <si>
-    <t>Q15,Create summary table.,,,,</t>
-  </si>
-  <si>
-    <t>Q16,Which expense increased the most?,,,,</t>
-  </si>
-  <si>
-    <t>Q17,Create quarterly summary.,,,,</t>
-  </si>
-  <si>
-    <t>Q18,% increase Jan to Jun.,,,,</t>
-  </si>
-  <si>
-    <t>Q19,Highest and lowest month.,,,,</t>
-  </si>
-  <si>
-    <t>Q20,Comparison chart.,,,,</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -181,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -495,206 +419,467 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3906E2B-B7DD-4861-82F9-599ABE7C4DCA}">
-  <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Scenario,Column1,Column2,Column3,Column4,Column5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Scenario 1: Choosing the Right Report Format,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Questions,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q1,Showing exact sales numbers for each product. Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q2,Comparing sales across 5 regions visually. Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q3,Executive overview of key metrics (sales, profit, customers). Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q4,Showing monthly sales trend over 12 months. Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Q5,Detailed transaction list for audit purposes. Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Q6,Showing each product's percentage contribution to total sales. Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q7,Comparing this year's sales vs last year's sales for each month. Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q8,Showing stock levels for 50 products at a glance. Which format is best? Why?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scenario 2: Weekly Sales Data,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Week,Product A,Product B,Product C,Product D,Total Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Week 1,1200,850,2100,950,5100</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Week 2,1300,900,2200,1000,5400</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Week 3,1250,880,2150,980,5260</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Week 4,1350,920,2300,1020,5590</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Q9,Create a table format report showing sales by product for each week.,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Q10,Create a bar chart description showing total sales by week. Which week had the highest sales?,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>36</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>• Various Data Reporting formats,</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q11,Create a line chart description showing sales trend for Product C over the 4 weeks.,,,,</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>